--- a/SNRN.xlsx
+++ b/SNRN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Automation\Desktop\Projects\Serial Number Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A303E594-240F-4A2B-94D0-704895BB8EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014BA8ED-9B82-49E9-9A8D-DD851CCB1928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{17FDB972-C9E2-4DA0-ADDD-D0A3289B9D96}"/>
+    <workbookView xWindow="5250" yWindow="1575" windowWidth="21600" windowHeight="11385" xr2:uid="{17FDB972-C9E2-4DA0-ADDD-D0A3289B9D96}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45E7EB96-60C1-4F14-B687-D77FD4D6192D}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -511,6 +511,166 @@
         <v>123123303</v>
       </c>
     </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>10000014</v>
+      </c>
+      <c r="B15">
+        <v>123123318</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>10000015</v>
+      </c>
+      <c r="B16">
+        <v>123123333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>10000016</v>
+      </c>
+      <c r="B17">
+        <v>123123348</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>10000017</v>
+      </c>
+      <c r="B18">
+        <v>123123363</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>10000018</v>
+      </c>
+      <c r="B19">
+        <v>123123378</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>10000019</v>
+      </c>
+      <c r="B20">
+        <v>123123393</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>10000020</v>
+      </c>
+      <c r="B21">
+        <v>123123408</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>10000021</v>
+      </c>
+      <c r="B22">
+        <v>123123423</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>10000022</v>
+      </c>
+      <c r="B23">
+        <v>123123438</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>10000023</v>
+      </c>
+      <c r="B24">
+        <v>123123453</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>10000024</v>
+      </c>
+      <c r="B25">
+        <v>123123468</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>10000025</v>
+      </c>
+      <c r="B26">
+        <v>123123483</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>10000026</v>
+      </c>
+      <c r="B27">
+        <v>123123498</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>10000027</v>
+      </c>
+      <c r="B28">
+        <v>123123513</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>10000028</v>
+      </c>
+      <c r="B29">
+        <v>123123528</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>10000029</v>
+      </c>
+      <c r="B30">
+        <v>123123543</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>10000030</v>
+      </c>
+      <c r="B31">
+        <v>123123558</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>10000031</v>
+      </c>
+      <c r="B32">
+        <v>123123573</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>10000032</v>
+      </c>
+      <c r="B33">
+        <v>123123588</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>10000033</v>
+      </c>
+      <c r="B34">
+        <v>123123603</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
